--- a/output/pdf_financials_xlsx/KENY.xlsx
+++ b/output/pdf_financials_xlsx/KENY.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005952</v>
       </c>
     </row>
     <row r="13">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.656942</v>
+        <v>-0.662894</v>
       </c>
     </row>
     <row r="28">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.656942</v>
+        <v>-0.662894</v>
       </c>
     </row>
     <row r="30">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/output/pdf_financials_xlsx/KENY.xlsx
+++ b/output/pdf_financials_xlsx/KENY.xlsx
@@ -783,10 +783,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="25">
@@ -800,10 +798,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="26">
@@ -817,10 +813,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>16.42355</v>
       </c>
     </row>
     <row r="27">
@@ -1025,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.012738</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.02245</v>
+        <v>0.009712</v>
       </c>
     </row>
     <row r="49">
@@ -1380,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.105929</v>
       </c>
     </row>
     <row r="69">
@@ -1649,10 +1643,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>1.889721</v>
       </c>
     </row>
     <row r="89">
@@ -1706,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.119715</v>
       </c>
     </row>
     <row r="93">
@@ -2460,7 +2454,11 @@
           <t>Receivables – Note 6</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -2602,7 +2600,11 @@
           <t>Accounts payable and accrued liabilities – Notes 8 and 11 $</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -2628,7 +2630,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -2652,7 +2658,11 @@
           <t>Reserves – Note 9</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3670,7 +3680,11 @@
           <t>Professional fees – Note 11</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -3898,7 +3912,11 @@
           <t>Loss per share – basic and diluted – Note 10 $</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KENY.xlsx
+++ b/output/pdf_financials_xlsx/KENY.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.120086</v>
+        <v>0.234086</v>
       </c>
     </row>
     <row r="8">
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
     </row>
     <row r="68">
@@ -3624,7 +3624,11 @@
           <t>Management and directors’ fees – Note 11</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
